--- a/Outputs/Recycling_Plot_Data/ACCII/05_Cumulative_Minerals_Lost_data_ACCII.xlsx
+++ b/Outputs/Recycling_Plot_Data/ACCII/05_Cumulative_Minerals_Lost_data_ACCII.xlsx
@@ -393,7 +393,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>7.168531207216345</v>
+        <v>7.084228248314997</v>
       </c>
     </row>
     <row r="3">
@@ -413,7 +413,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>4.570895205174093</v>
+        <v>4.528479508768241</v>
       </c>
     </row>
     <row r="4">
@@ -433,7 +433,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>16.47277137808431</v>
+        <v>16.30503910633811</v>
       </c>
     </row>
     <row r="5">
@@ -453,7 +453,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>174.426983251049</v>
+        <v>172.7050374246679</v>
       </c>
     </row>
   </sheetData>
